--- a/analise_modelos.xlsx
+++ b/analise_modelos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mateus Santos Rochas\Desktop\Estudos\07. Doutorado - Matemática aplicada\Pesquisa\Dados Novos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74372127-B35D-4255-B669-6784AC4C63D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B285C06B-7DB7-4328-8FB6-6082268D5824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7D832D6A-9761-4376-BF9C-32F029621992}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7D832D6A-9761-4376-BF9C-32F029621992}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -382,7 +382,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5F4CDD86-DF7B-498D-B09C-26FF52242A0B}" name="Tabela1" displayName="Tabela1" ref="A1:M34" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
   <autoFilter ref="A1:M34" xr:uid="{5F4CDD86-DF7B-498D-B09C-26FF52242A0B}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M34">
-    <sortCondition descending="1" ref="M1:M34"/>
+    <sortCondition descending="1" ref="J1:J34"/>
   </sortState>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{DB6B634D-618C-48A3-91D1-35F67210BB4B}" name="Tipo Modelo" dataDxfId="12"/>
@@ -779,12 +779,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>39</v>
@@ -796,36 +796,36 @@
         <v>45</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>53</v>
+        <v>45</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="H2" s="7">
-        <v>2.7298484167170911</v>
+        <v>2.7493620270485879</v>
       </c>
       <c r="I2" s="7">
-        <v>7.6201363267733608</v>
+        <v>7.0920830881489447</v>
       </c>
       <c r="J2" s="7">
-        <v>0.453720098786627</v>
+        <v>0.52680802574029384</v>
       </c>
       <c r="K2" s="7">
-        <v>96.054323433514625</v>
+        <v>80.507026241591291</v>
       </c>
       <c r="L2" s="7">
-        <v>26.81506535822751</v>
+        <v>25.42678963121066</v>
       </c>
       <c r="M2" s="7">
-        <v>28.84570835534058</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>18.507399067819382</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>39</v>
@@ -837,36 +837,36 @@
         <v>0.3</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>53</v>
+        <v>45</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="H3" s="7">
-        <v>2.7161012925836912</v>
+        <v>2.743637835672772</v>
       </c>
       <c r="I3" s="7">
-        <v>7.6105760128162601</v>
+        <v>7.0983314926155421</v>
       </c>
       <c r="J3" s="7">
-        <v>0.45508997747841889</v>
+        <v>0.52597385690976839</v>
       </c>
       <c r="K3" s="7">
-        <v>96.054377210573222</v>
+        <v>80.669836286500512</v>
       </c>
       <c r="L3" s="7">
-        <v>27.014714726197639</v>
+        <v>25.528757967724701</v>
       </c>
       <c r="M3" s="7">
-        <v>28.61745074237777</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+        <v>18.957119073873312</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>39</v>
@@ -878,36 +878,36 @@
         <v>0.4</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>52</v>
+        <v>45</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="H4" s="7">
-        <v>2.6388373415659929</v>
+        <v>2.7406700786101461</v>
       </c>
       <c r="I4" s="7">
-        <v>7.5624888465034994</v>
+        <v>7.1085872102701009</v>
       </c>
       <c r="J4" s="7">
-        <v>0.46195421400563008</v>
+        <v>0.52460311500008683</v>
       </c>
       <c r="K4" s="7">
-        <v>96.111811109157202</v>
+        <v>81.354660239232629</v>
       </c>
       <c r="L4" s="7">
-        <v>27.20121249621964</v>
+        <v>25.746715287023491</v>
       </c>
       <c r="M4" s="7">
-        <v>26.342596453512972</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+        <v>19.42197388782327</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>39</v>
@@ -915,40 +915,40 @@
       <c r="D5" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>45</v>
+      <c r="E5" s="2">
+        <v>0.5</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>52</v>
+        <v>45</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="H5" s="7">
-        <v>2.64981685188704</v>
+        <v>2.7310233686044452</v>
       </c>
       <c r="I5" s="7">
-        <v>7.5745072714927417</v>
+        <v>7.1415331764288661</v>
       </c>
       <c r="J5" s="7">
-        <v>0.46024271363773023</v>
+        <v>0.52018628665366828</v>
       </c>
       <c r="K5" s="7">
-        <v>96.11175733209862</v>
+        <v>82.139563298017933</v>
       </c>
       <c r="L5" s="7">
-        <v>27.01813298293305</v>
+        <v>26.1234187665771</v>
       </c>
       <c r="M5" s="7">
-        <v>26.25333197428936</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>19.915245075782149</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>39</v>
@@ -957,39 +957,39 @@
         <v>41</v>
       </c>
       <c r="E6" s="2">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H6" s="7">
-        <v>2.6569306187208559</v>
+        <v>2.4682266188321029</v>
       </c>
       <c r="I6" s="7">
-        <v>7.2804051252924511</v>
+        <v>7.1431772282464863</v>
       </c>
       <c r="J6" s="7">
-        <v>0.50134424742944561</v>
+        <v>0.51996534546714879</v>
       </c>
       <c r="K6" s="7">
-        <v>94.506001250854382</v>
+        <v>94.56840952735881</v>
       </c>
       <c r="L6" s="7">
-        <v>24.779116884681919</v>
+        <v>26.695252562823502</v>
       </c>
       <c r="M6" s="7">
-        <v>23.051547920199411</v>
+        <v>19.313250369876169</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>39</v>
@@ -997,40 +997,40 @@
       <c r="D7" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>45</v>
+      <c r="E7" s="2">
+        <v>0.5</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>49</v>
       </c>
       <c r="H7" s="7">
-        <v>2.6770025161903162</v>
+        <v>2.4756224951358652</v>
       </c>
       <c r="I7" s="7">
-        <v>7.2881507197461568</v>
+        <v>7.1490489543975704</v>
       </c>
       <c r="J7" s="7">
-        <v>0.50028264721540228</v>
+        <v>0.51917583950672985</v>
       </c>
       <c r="K7" s="7">
-        <v>94.507076792026368</v>
+        <v>94.513368707882478</v>
       </c>
       <c r="L7" s="7">
-        <v>24.472690446146231</v>
+        <v>26.63134854283771</v>
       </c>
       <c r="M7" s="7">
-        <v>22.688930277955379</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+        <v>19.017349431826961</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>39</v>
@@ -1038,122 +1038,122 @@
       <c r="D8" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="H8" s="7">
+        <v>2.4779713845906519</v>
+      </c>
+      <c r="I8" s="7">
+        <v>7.1506094042261932</v>
+      </c>
+      <c r="J8" s="7">
+        <v>0.51896591399936631</v>
+      </c>
+      <c r="K8" s="7">
+        <v>94.567253320598923</v>
+      </c>
+      <c r="L8" s="7">
+        <v>26.437840449680369</v>
+      </c>
+      <c r="M8" s="7">
+        <v>18.85858838573375</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>5</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9" s="7">
+        <v>2.488888492807424</v>
+      </c>
+      <c r="I9" s="7">
+        <v>7.1553689678932049</v>
+      </c>
+      <c r="J9" s="7">
+        <v>0.51832533242163981</v>
+      </c>
+      <c r="K9" s="7">
+        <v>94.515573567285045</v>
+      </c>
+      <c r="L9" s="7">
+        <v>26.271968093180519</v>
+      </c>
+      <c r="M9" s="7">
+        <v>18.556201101443371</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>7</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="2">
         <v>0.9</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H8" s="7">
-        <v>3.0278488612667172</v>
-      </c>
-      <c r="I8" s="7">
-        <v>8.3225698872581546</v>
-      </c>
-      <c r="J8" s="7">
-        <v>0.34836464159339908</v>
-      </c>
-      <c r="K8" s="7">
-        <v>87.85165490831281</v>
-      </c>
-      <c r="L8" s="7">
-        <v>27.76788993908551</v>
-      </c>
-      <c r="M8" s="7">
-        <v>21.19707064248804</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
-        <v>3</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E9" s="2">
-        <v>0.75</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H9" s="7">
-        <v>2.833619405217993</v>
-      </c>
-      <c r="I9" s="7">
-        <v>7.5817225415104001</v>
-      </c>
-      <c r="J9" s="7">
-        <v>0.45921390758597053</v>
-      </c>
-      <c r="K9" s="7">
-        <v>85.090391168946539</v>
-      </c>
-      <c r="L9" s="7">
-        <v>27.183252164220011</v>
-      </c>
-      <c r="M9" s="7">
-        <v>21.108732784156022</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
-        <v>6</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E10" s="2">
-        <v>0.75</v>
-      </c>
       <c r="F10" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H10" s="7">
-        <v>2.6065907643898489</v>
+        <v>2.4627856480329191</v>
       </c>
       <c r="I10" s="7">
-        <v>7.342069801503941</v>
+        <v>7.1755828355908129</v>
       </c>
       <c r="J10" s="7">
-        <v>0.49286129403783713</v>
+        <v>0.51560003318654712</v>
       </c>
       <c r="K10" s="7">
-        <v>94.560665630920511</v>
+        <v>94.933824640540692</v>
       </c>
       <c r="L10" s="7">
-        <v>25.140003684764888</v>
+        <v>26.766456588718821</v>
       </c>
       <c r="M10" s="7">
-        <v>20.202806425807012</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+        <v>19.074182179844762</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>39</v>
@@ -1161,155 +1161,155 @@
       <c r="D11" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E11" s="2">
-        <v>0.5</v>
+      <c r="E11" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>51</v>
       </c>
       <c r="H11" s="7">
-        <v>2.7310233686044452</v>
+        <v>2.4674289905153119</v>
       </c>
       <c r="I11" s="7">
-        <v>7.1415331764288661</v>
+        <v>7.1790057368284206</v>
       </c>
       <c r="J11" s="7">
-        <v>0.52018628665366828</v>
+        <v>0.51513778538125332</v>
       </c>
       <c r="K11" s="7">
-        <v>82.139563298017933</v>
+        <v>94.933932194657899</v>
       </c>
       <c r="L11" s="7">
-        <v>26.1234187665771</v>
+        <v>26.579553262812961</v>
       </c>
       <c r="M11" s="7">
-        <v>19.915245075782149</v>
+        <v>18.850248797709391</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
+        <v>7</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="H12" s="7">
+        <v>2.4535201049942512</v>
+      </c>
+      <c r="I12" s="7">
+        <v>7.2159456000193831</v>
+      </c>
+      <c r="J12" s="7">
+        <v>0.51013519177434441</v>
+      </c>
+      <c r="K12" s="7">
+        <v>96.0551300893936</v>
+      </c>
+      <c r="L12" s="7">
+        <v>27.052025867512999</v>
+      </c>
+      <c r="M12" s="7">
+        <v>18.956192452981711</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>5</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="H13" s="7">
+        <v>2.4604493754743428</v>
+      </c>
+      <c r="I13" s="7">
+        <v>7.2213972523929719</v>
+      </c>
+      <c r="J13" s="7">
+        <v>0.50939472570034172</v>
+      </c>
+      <c r="K13" s="7">
+        <v>96.0551300893936</v>
+      </c>
+      <c r="L13" s="7">
+        <v>26.917265440960911</v>
+      </c>
+      <c r="M13" s="7">
+        <v>18.896270968658591</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>1</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="H12" s="7">
-        <v>2.6232561371412531</v>
-      </c>
-      <c r="I12" s="7">
-        <v>7.3604526235800343</v>
-      </c>
-      <c r="J12" s="7">
-        <v>0.49031860193450633</v>
-      </c>
-      <c r="K12" s="7">
-        <v>94.560558076803318</v>
-      </c>
-      <c r="L12" s="7">
-        <v>24.839486774822628</v>
-      </c>
-      <c r="M12" s="7">
-        <v>19.504443147175191</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
-        <v>3</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E13" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H13" s="7">
-        <v>2.7406700786101461</v>
-      </c>
-      <c r="I13" s="7">
-        <v>7.1085872102701009</v>
-      </c>
-      <c r="J13" s="7">
-        <v>0.52460311500008683</v>
-      </c>
-      <c r="K13" s="7">
-        <v>81.354660239232629</v>
-      </c>
-      <c r="L13" s="7">
-        <v>25.746715287023491</v>
-      </c>
-      <c r="M13" s="7">
-        <v>19.42197388782327</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
-        <v>7</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="C14" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E14" s="2">
-        <v>0.75</v>
+      <c r="E14" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>50</v>
+        <v>45</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="H14" s="7">
-        <v>2.4682266188321029</v>
+        <v>2.8567363468837268</v>
       </c>
       <c r="I14" s="7">
-        <v>7.1431772282464863</v>
+        <v>7.2216265848902577</v>
       </c>
       <c r="J14" s="7">
-        <v>0.51996534546714879</v>
+        <v>0.50936356455095733</v>
       </c>
       <c r="K14" s="7">
-        <v>94.56840952735881</v>
+        <v>77.500108898543658</v>
       </c>
       <c r="L14" s="7">
-        <v>26.695252562823502</v>
+        <v>25.463811089751839</v>
       </c>
       <c r="M14" s="7">
-        <v>19.313250369876169</v>
+        <v>18.179684145825419</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -1355,10 +1355,10 @@
     </row>
     <row r="16" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>39</v>
@@ -1366,40 +1366,40 @@
       <c r="D16" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E16" s="2">
-        <v>0.9</v>
+      <c r="E16" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>47</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H16" s="7">
-        <v>2.4627856480329191</v>
+        <v>2.457807637536503</v>
       </c>
       <c r="I16" s="7">
-        <v>7.1755828355908129</v>
+        <v>7.231196297621949</v>
       </c>
       <c r="J16" s="7">
-        <v>0.51560003318654712</v>
+        <v>0.5080623727392648</v>
       </c>
       <c r="K16" s="7">
-        <v>94.933824640540692</v>
+        <v>96.112563987977609</v>
       </c>
       <c r="L16" s="7">
-        <v>26.766456588718821</v>
+        <v>26.918771791386689</v>
       </c>
       <c r="M16" s="7">
-        <v>19.074182179844762</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+        <v>19.03557297602832</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>39</v>
@@ -1407,40 +1407,40 @@
       <c r="D17" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>45</v>
+      <c r="E17" s="2">
+        <v>0.5</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H17" s="7">
-        <v>2.457807637536503</v>
+        <v>2.6569306187208559</v>
       </c>
       <c r="I17" s="7">
-        <v>7.231196297621949</v>
+        <v>7.2804051252924511</v>
       </c>
       <c r="J17" s="7">
-        <v>0.5080623727392648</v>
+        <v>0.50134424742944561</v>
       </c>
       <c r="K17" s="7">
-        <v>96.112563987977609</v>
+        <v>94.506001250854382</v>
       </c>
       <c r="L17" s="7">
-        <v>26.918771791386689</v>
+        <v>24.779116884681919</v>
       </c>
       <c r="M17" s="7">
-        <v>19.03557297602832</v>
+        <v>23.051547920199411</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>39</v>
@@ -1448,40 +1448,40 @@
       <c r="D18" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E18" s="2">
-        <v>0.5</v>
+      <c r="E18" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>49</v>
       </c>
       <c r="H18" s="7">
-        <v>2.4756224951358652</v>
+        <v>2.6770025161903162</v>
       </c>
       <c r="I18" s="7">
-        <v>7.1490489543975704</v>
+        <v>7.2881507197461568</v>
       </c>
       <c r="J18" s="7">
-        <v>0.51917583950672985</v>
+        <v>0.50028264721540228</v>
       </c>
       <c r="K18" s="7">
-        <v>94.513368707882478</v>
+        <v>94.507076792026368</v>
       </c>
       <c r="L18" s="7">
-        <v>26.63134854283771</v>
+        <v>24.472690446146231</v>
       </c>
       <c r="M18" s="7">
-        <v>19.017349431826961</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22.688930277955379</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>39</v>
@@ -1490,39 +1490,39 @@
         <v>41</v>
       </c>
       <c r="E19" s="2">
-        <v>0.3</v>
+        <v>0.75</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>50</v>
       </c>
       <c r="H19" s="7">
-        <v>2.743637835672772</v>
+        <v>2.6065907643898489</v>
       </c>
       <c r="I19" s="7">
-        <v>7.0983314926155421</v>
+        <v>7.342069801503941</v>
       </c>
       <c r="J19" s="7">
-        <v>0.52597385690976839</v>
+        <v>0.49286129403783713</v>
       </c>
       <c r="K19" s="7">
-        <v>80.669836286500512</v>
+        <v>94.560665630920511</v>
       </c>
       <c r="L19" s="7">
-        <v>25.528757967724701</v>
+        <v>25.140003684764888</v>
       </c>
       <c r="M19" s="7">
-        <v>18.957119073873312</v>
+        <v>20.202806425807012</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>39</v>
@@ -1530,81 +1530,81 @@
       <c r="D20" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E20" s="2">
-        <v>0.3</v>
+      <c r="E20" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="H20" s="7">
-        <v>2.4535201049942512</v>
+        <v>2.6232561371412531</v>
       </c>
       <c r="I20" s="7">
-        <v>7.2159456000193831</v>
+        <v>7.3604526235800343</v>
       </c>
       <c r="J20" s="7">
-        <v>0.51013519177434441</v>
+        <v>0.49031860193450633</v>
       </c>
       <c r="K20" s="7">
-        <v>96.0551300893936</v>
+        <v>94.560558076803318</v>
       </c>
       <c r="L20" s="7">
-        <v>27.052025867512999</v>
+        <v>24.839486774822628</v>
       </c>
       <c r="M20" s="7">
-        <v>18.956192452981711</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>19.504443147175191</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>45</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>53</v>
+        <v>45</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="H21" s="7">
-        <v>2.4604493754743428</v>
+        <v>3.1706289835191348</v>
       </c>
       <c r="I21" s="7">
-        <v>7.2213972523929719</v>
+        <v>7.5354277985963449</v>
       </c>
       <c r="J21" s="7">
-        <v>0.50939472570034172</v>
+        <v>0.4657979307309279</v>
       </c>
       <c r="K21" s="7">
-        <v>96.0551300893936</v>
+        <v>6.9377514413596133</v>
       </c>
       <c r="L21" s="7">
-        <v>26.917265440960911</v>
+        <v>24.771411322888529</v>
       </c>
       <c r="M21" s="7">
-        <v>18.896270968658591</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>9.7119135648032326</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>39</v>
@@ -1612,40 +1612,40 @@
       <c r="D22" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>45</v>
+      <c r="E22" s="2">
+        <v>0.9</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H22" s="7">
-        <v>2.4779713845906519</v>
+        <v>2.5413627264017919</v>
       </c>
       <c r="I22" s="7">
-        <v>7.1506094042261932</v>
+        <v>7.5601813866822871</v>
       </c>
       <c r="J22" s="7">
-        <v>0.51896591399936631</v>
+        <v>0.46228250001114007</v>
       </c>
       <c r="K22" s="7">
-        <v>94.567253320598923</v>
+        <v>94.931350895845128</v>
       </c>
       <c r="L22" s="7">
-        <v>26.437840449680369</v>
+        <v>26.147114817505649</v>
       </c>
       <c r="M22" s="7">
-        <v>18.85858838573375</v>
+        <v>12.523281349901319</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>39</v>
@@ -1653,81 +1653,81 @@
       <c r="D23" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>45</v>
+      <c r="E23" s="2">
+        <v>0.4</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G23" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="H23" s="7">
+        <v>2.6388373415659929</v>
+      </c>
+      <c r="I23" s="7">
+        <v>7.5624888465034994</v>
+      </c>
+      <c r="J23" s="7">
+        <v>0.46195421400563008</v>
+      </c>
+      <c r="K23" s="7">
+        <v>96.111811109157202</v>
+      </c>
+      <c r="L23" s="7">
+        <v>27.20121249621964</v>
+      </c>
+      <c r="M23" s="7">
+        <v>26.342596453512972</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>4</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G24" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="H23" s="7">
-        <v>2.4674289905153119</v>
-      </c>
-      <c r="I23" s="7">
-        <v>7.1790057368284206</v>
-      </c>
-      <c r="J23" s="7">
-        <v>0.51513778538125332</v>
-      </c>
-      <c r="K23" s="7">
-        <v>94.933932194657899</v>
-      </c>
-      <c r="L23" s="7">
-        <v>26.579553262812961</v>
-      </c>
-      <c r="M23" s="7">
-        <v>18.850248797709391</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
-        <v>5</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>49</v>
-      </c>
       <c r="H24" s="7">
-        <v>2.488888492807424</v>
+        <v>2.5506766195903761</v>
       </c>
       <c r="I24" s="7">
-        <v>7.1553689678932049</v>
+        <v>7.5698398165558478</v>
       </c>
       <c r="J24" s="7">
-        <v>0.51832533242163981</v>
+        <v>0.46090771177406492</v>
       </c>
       <c r="K24" s="7">
-        <v>94.515573567285045</v>
+        <v>94.931243341727935</v>
       </c>
       <c r="L24" s="7">
-        <v>26.271968093180519</v>
+        <v>25.900768586336479</v>
       </c>
       <c r="M24" s="7">
-        <v>18.556201101443371</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+        <v>12.242515219748141</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>39</v>
@@ -1739,45 +1739,45 @@
         <v>45</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>52</v>
       </c>
       <c r="H25" s="7">
-        <v>2.7493620270485879</v>
+        <v>2.64981685188704</v>
       </c>
       <c r="I25" s="7">
-        <v>7.0920830881489447</v>
+        <v>7.5745072714927417</v>
       </c>
       <c r="J25" s="7">
-        <v>0.52680802574029384</v>
+        <v>0.46024271363773023</v>
       </c>
       <c r="K25" s="7">
-        <v>80.507026241591291</v>
+        <v>96.11175733209862</v>
       </c>
       <c r="L25" s="7">
-        <v>25.42678963121066</v>
+        <v>27.01813298293305</v>
       </c>
       <c r="M25" s="7">
-        <v>18.507399067819382</v>
+        <v>26.25333197428936</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>45</v>
+      <c r="E26" s="2">
+        <v>0.75</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>45</v>
@@ -1786,30 +1786,30 @@
         <v>45</v>
       </c>
       <c r="H26" s="7">
-        <v>2.8567363468837268</v>
+        <v>2.833619405217993</v>
       </c>
       <c r="I26" s="7">
-        <v>7.2216265848902577</v>
+        <v>7.5817225415104001</v>
       </c>
       <c r="J26" s="7">
-        <v>0.50936356455095733</v>
+        <v>0.45921390758597053</v>
       </c>
       <c r="K26" s="7">
-        <v>77.500108898543658</v>
+        <v>85.090391168946539</v>
       </c>
       <c r="L26" s="7">
-        <v>25.463811089751839</v>
+        <v>27.183252164220011</v>
       </c>
       <c r="M26" s="7">
-        <v>18.179684145825419</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+        <v>21.108732784156022</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>6</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>39</v>
@@ -1818,42 +1818,42 @@
         <v>41</v>
       </c>
       <c r="E27" s="2">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>46</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H27" s="7">
-        <v>2.5413627264017919</v>
+        <v>2.7161012925836912</v>
       </c>
       <c r="I27" s="7">
-        <v>7.5601813866822871</v>
+        <v>7.6105760128162601</v>
       </c>
       <c r="J27" s="7">
-        <v>0.46228250001114007</v>
+        <v>0.45508997747841889</v>
       </c>
       <c r="K27" s="7">
-        <v>94.931350895845128</v>
+        <v>96.054377210573222</v>
       </c>
       <c r="L27" s="7">
-        <v>26.147114817505649</v>
+        <v>27.014714726197639</v>
       </c>
       <c r="M27" s="7">
-        <v>12.523281349901319</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+        <v>28.61745074237777</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>41</v>
@@ -1862,83 +1862,83 @@
         <v>45</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>53</v>
       </c>
       <c r="H28" s="7">
-        <v>3.226563230616541</v>
+        <v>2.7298484167170911</v>
       </c>
       <c r="I28" s="7">
-        <v>7.8592197344466506</v>
+        <v>7.6201363267733608</v>
       </c>
       <c r="J28" s="7">
-        <v>0.41890304107121262</v>
+        <v>0.453720098786627</v>
       </c>
       <c r="K28" s="7">
-        <v>75.401539852295926</v>
+        <v>96.054323433514625</v>
       </c>
       <c r="L28" s="7">
-        <v>20.045932100675191</v>
+        <v>26.81506535822751</v>
       </c>
       <c r="M28" s="7">
-        <v>12.336412803429729</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+        <v>28.84570835534058</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>45</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>51</v>
+        <v>45</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="H29" s="7">
-        <v>2.5506766195903761</v>
+        <v>3.2163354847420331</v>
       </c>
       <c r="I29" s="7">
-        <v>7.5698398165558478</v>
+        <v>7.6333724393211861</v>
       </c>
       <c r="J29" s="7">
-        <v>0.46090771177406492</v>
+        <v>0.45182068341932141</v>
       </c>
       <c r="K29" s="7">
-        <v>94.931243341727935</v>
+        <v>3.3728433382862</v>
       </c>
       <c r="L29" s="7">
-        <v>25.900768586336479</v>
+        <v>24.520661913551709</v>
       </c>
       <c r="M29" s="7">
-        <v>12.242515219748141</v>
+        <v>9.4536952096788642</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>45</v>
@@ -1950,22 +1950,22 @@
         <v>45</v>
       </c>
       <c r="H30" s="7">
-        <v>3.1706289835191348</v>
+        <v>3.226563230616541</v>
       </c>
       <c r="I30" s="7">
-        <v>7.5354277985963449</v>
+        <v>7.8592197344466506</v>
       </c>
       <c r="J30" s="7">
-        <v>0.4657979307309279</v>
+        <v>0.41890304107121262</v>
       </c>
       <c r="K30" s="7">
-        <v>6.9377514413596133</v>
+        <v>75.401539852295926</v>
       </c>
       <c r="L30" s="7">
-        <v>24.771411322888529</v>
+        <v>20.045932100675191</v>
       </c>
       <c r="M30" s="7">
-        <v>9.7119135648032326</v>
+        <v>12.336412803429729</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
@@ -1973,7 +1973,7 @@
         <v>2</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>39</v>
@@ -1991,39 +1991,39 @@
         <v>45</v>
       </c>
       <c r="H31" s="7">
-        <v>3.2163354847420331</v>
+        <v>3.4996060522041521</v>
       </c>
       <c r="I31" s="7">
-        <v>7.6333724393211861</v>
+        <v>8.2967692939284348</v>
       </c>
       <c r="J31" s="7">
-        <v>0.45182068341932141</v>
+        <v>0.35239861643017739</v>
       </c>
       <c r="K31" s="7">
-        <v>3.3728433382862</v>
+        <v>9.305474665896579</v>
       </c>
       <c r="L31" s="7">
-        <v>24.520661913551709</v>
+        <v>21.806160509748981</v>
       </c>
       <c r="M31" s="7">
-        <v>9.4536952096788642</v>
+        <v>5.0052971827636163</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
+      </c>
+      <c r="E32" s="2">
+        <v>0.9</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>45</v>
@@ -2032,22 +2032,22 @@
         <v>45</v>
       </c>
       <c r="H32" s="7">
-        <v>3.4996060522041521</v>
+        <v>3.0278488612667172</v>
       </c>
       <c r="I32" s="7">
-        <v>8.2967692939284348</v>
+        <v>8.3225698872581546</v>
       </c>
       <c r="J32" s="7">
-        <v>0.35239861643017739</v>
+        <v>0.34836464159339908</v>
       </c>
       <c r="K32" s="7">
-        <v>9.305474665896579</v>
+        <v>87.85165490831281</v>
       </c>
       <c r="L32" s="7">
-        <v>21.806160509748981</v>
+        <v>27.76788993908551</v>
       </c>
       <c r="M32" s="7">
-        <v>5.0052971827636163</v>
+        <v>21.19707064248804</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">

--- a/analise_modelos.xlsx
+++ b/analise_modelos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mateus Santos Rochas\Desktop\Estudos\07. Doutorado - Matemática aplicada\Pesquisa\Dados Novos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B285C06B-7DB7-4328-8FB6-6082268D5824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24EEEB37-1642-451B-8FB1-39A2EC537B1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7D832D6A-9761-4376-BF9C-32F029621992}"/>
+    <workbookView xWindow="28695" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{7D832D6A-9761-4376-BF9C-32F029621992}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -380,9 +380,16 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5F4CDD86-DF7B-498D-B09C-26FF52242A0B}" name="Tabela1" displayName="Tabela1" ref="A1:M34" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
-  <autoFilter ref="A1:M34" xr:uid="{5F4CDD86-DF7B-498D-B09C-26FF52242A0B}"/>
+  <autoFilter ref="A1:M34" xr:uid="{5F4CDD86-DF7B-498D-B09C-26FF52242A0B}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="4"/>
+        <filter val="5"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M34">
-    <sortCondition descending="1" ref="J1:J34"/>
+    <sortCondition ref="B1:B34"/>
   </sortState>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{DB6B634D-618C-48A3-91D1-35F67210BB4B}" name="Tipo Modelo" dataDxfId="12"/>
@@ -723,13 +730,13 @@
   <dimension ref="A1:M34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.7109375" style="2" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="33.28515625" style="1" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="9" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="33.7109375" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="27.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.5703125" customWidth="1"/>
     <col min="8" max="8" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="5.7109375" bestFit="1" customWidth="1"/>
@@ -779,627 +786,627 @@
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2" s="7">
+        <v>5.4602967883730509</v>
+      </c>
+      <c r="I2" s="7">
+        <v>10.15019361435558</v>
+      </c>
+      <c r="J2" s="7">
+        <v>3.074423462670994E-2</v>
+      </c>
+      <c r="K2" s="7">
+        <v>6.4286978046591363</v>
+      </c>
+      <c r="L2" s="7">
+        <v>11.641076090394931</v>
+      </c>
+      <c r="M2" s="7">
+        <v>0.47350327560485178</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H3" s="7">
+        <v>3.226563230616541</v>
+      </c>
+      <c r="I3" s="7">
+        <v>7.8592197344466506</v>
+      </c>
+      <c r="J3" s="7">
+        <v>0.41890304107121262</v>
+      </c>
+      <c r="K3" s="7">
+        <v>75.401539852295926</v>
+      </c>
+      <c r="L3" s="7">
+        <v>20.045932100675191</v>
+      </c>
+      <c r="M3" s="7">
+        <v>12.336412803429729</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H4" s="7">
+        <v>2.8567363468837268</v>
+      </c>
+      <c r="I4" s="7">
+        <v>7.2216265848902577</v>
+      </c>
+      <c r="J4" s="7">
+        <v>0.50936356455095733</v>
+      </c>
+      <c r="K4" s="7">
+        <v>77.500108898543658</v>
+      </c>
+      <c r="L4" s="7">
+        <v>25.463811089751839</v>
+      </c>
+      <c r="M4" s="7">
+        <v>18.179684145825419</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H2" s="7">
+      <c r="C5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H5" s="7">
         <v>2.7493620270485879</v>
       </c>
-      <c r="I2" s="7">
+      <c r="I5" s="7">
         <v>7.0920830881489447</v>
       </c>
-      <c r="J2" s="7">
+      <c r="J5" s="7">
         <v>0.52680802574029384</v>
       </c>
-      <c r="K2" s="7">
+      <c r="K5" s="7">
         <v>80.507026241591291</v>
       </c>
-      <c r="L2" s="7">
+      <c r="L5" s="7">
         <v>25.42678963121066</v>
       </c>
-      <c r="M2" s="7">
+      <c r="M5" s="7">
         <v>18.507399067819382</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
+    <row r="6" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>2</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="7">
+        <v>4.4554620546761843</v>
+      </c>
+      <c r="I6" s="7">
+        <v>10.32948531598924</v>
+      </c>
+      <c r="J6" s="7">
+        <v>-3.7998009942659121E-3</v>
+      </c>
+      <c r="K6" s="7">
+        <v>1.791690261351127</v>
+      </c>
+      <c r="L6" s="7">
+        <v>17.656280959846491</v>
+      </c>
+      <c r="M6" s="7">
+        <v>0.16215865602905891</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>2</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" s="7">
+        <v>3.4996060522041521</v>
+      </c>
+      <c r="I7" s="7">
+        <v>8.2967692939284348</v>
+      </c>
+      <c r="J7" s="7">
+        <v>0.35239861643017739</v>
+      </c>
+      <c r="K7" s="7">
+        <v>9.305474665896579</v>
+      </c>
+      <c r="L7" s="7">
+        <v>21.806160509748981</v>
+      </c>
+      <c r="M7" s="7">
+        <v>5.0052971827636163</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>2</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H8" s="7">
+        <v>3.2163354847420331</v>
+      </c>
+      <c r="I8" s="7">
+        <v>7.6333724393211861</v>
+      </c>
+      <c r="J8" s="7">
+        <v>0.45182068341932141</v>
+      </c>
+      <c r="K8" s="7">
+        <v>3.3728433382862</v>
+      </c>
+      <c r="L8" s="7">
+        <v>24.520661913551709</v>
+      </c>
+      <c r="M8" s="7">
+        <v>9.4536952096788642</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>2</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H9" s="7">
+        <v>3.1706289835191348</v>
+      </c>
+      <c r="I9" s="7">
+        <v>7.5354277985963449</v>
+      </c>
+      <c r="J9" s="7">
+        <v>0.4657979307309279</v>
+      </c>
+      <c r="K9" s="7">
+        <v>6.9377514413596133</v>
+      </c>
+      <c r="L9" s="7">
+        <v>24.771411322888529</v>
+      </c>
+      <c r="M9" s="7">
+        <v>9.7119135648032326</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
         <v>3</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H10" s="7">
+        <v>2.7310233686044452</v>
+      </c>
+      <c r="I10" s="7">
+        <v>7.1415331764288661</v>
+      </c>
+      <c r="J10" s="7">
+        <v>0.52018628665366828</v>
+      </c>
+      <c r="K10" s="7">
+        <v>82.139563298017933</v>
+      </c>
+      <c r="L10" s="7">
+        <v>26.1234187665771</v>
+      </c>
+      <c r="M10" s="7">
+        <v>19.915245075782149</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>3</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H11" s="7">
+        <v>2.833619405217993</v>
+      </c>
+      <c r="I11" s="7">
+        <v>7.5817225415104001</v>
+      </c>
+      <c r="J11" s="7">
+        <v>0.45921390758597053</v>
+      </c>
+      <c r="K11" s="7">
+        <v>85.090391168946539</v>
+      </c>
+      <c r="L11" s="7">
+        <v>27.183252164220011</v>
+      </c>
+      <c r="M11" s="7">
+        <v>21.108732784156022</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>3</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H12" s="7">
+        <v>3.0278488612667172</v>
+      </c>
+      <c r="I12" s="7">
+        <v>8.3225698872581546</v>
+      </c>
+      <c r="J12" s="7">
+        <v>0.34836464159339908</v>
+      </c>
+      <c r="K12" s="7">
+        <v>87.85165490831281</v>
+      </c>
+      <c r="L12" s="7">
+        <v>27.76788993908551</v>
+      </c>
+      <c r="M12" s="7">
+        <v>21.19707064248804</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>3</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H13" s="7">
+        <v>2.7406700786101461</v>
+      </c>
+      <c r="I13" s="7">
+        <v>7.1085872102701009</v>
+      </c>
+      <c r="J13" s="7">
+        <v>0.52460311500008683</v>
+      </c>
+      <c r="K13" s="7">
+        <v>81.354660239232629</v>
+      </c>
+      <c r="L13" s="7">
+        <v>25.746715287023491</v>
+      </c>
+      <c r="M13" s="7">
+        <v>19.42197388782327</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>3</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E3" s="2">
+      <c r="C14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E14" s="2">
         <v>0.3</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H3" s="7">
+      <c r="F14" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H14" s="7">
         <v>2.743637835672772</v>
       </c>
-      <c r="I3" s="7">
+      <c r="I14" s="7">
         <v>7.0983314926155421</v>
       </c>
-      <c r="J3" s="7">
+      <c r="J14" s="7">
         <v>0.52597385690976839</v>
       </c>
-      <c r="K3" s="7">
+      <c r="K14" s="7">
         <v>80.669836286500512</v>
       </c>
-      <c r="L3" s="7">
+      <c r="L14" s="7">
         <v>25.528757967724701</v>
       </c>
-      <c r="M3" s="7">
+      <c r="M14" s="7">
         <v>18.957119073873312</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E4" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H4" s="7">
-        <v>2.7406700786101461</v>
-      </c>
-      <c r="I4" s="7">
-        <v>7.1085872102701009</v>
-      </c>
-      <c r="J4" s="7">
-        <v>0.52460311500008683</v>
-      </c>
-      <c r="K4" s="7">
-        <v>81.354660239232629</v>
-      </c>
-      <c r="L4" s="7">
-        <v>25.746715287023491</v>
-      </c>
-      <c r="M4" s="7">
-        <v>19.42197388782327</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E5" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H5" s="7">
-        <v>2.7310233686044452</v>
-      </c>
-      <c r="I5" s="7">
-        <v>7.1415331764288661</v>
-      </c>
-      <c r="J5" s="7">
-        <v>0.52018628665366828</v>
-      </c>
-      <c r="K5" s="7">
-        <v>82.139563298017933</v>
-      </c>
-      <c r="L5" s="7">
-        <v>26.1234187665771</v>
-      </c>
-      <c r="M5" s="7">
-        <v>19.915245075782149</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
-        <v>7</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0.75</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G6" s="6" t="s">
+    <row r="15" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>4</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H15" s="7">
+        <v>2.6770025161903162</v>
+      </c>
+      <c r="I15" s="7">
+        <v>7.2881507197461568</v>
+      </c>
+      <c r="J15" s="7">
+        <v>0.50028264721540228</v>
+      </c>
+      <c r="K15" s="7">
+        <v>94.507076792026368</v>
+      </c>
+      <c r="L15" s="7">
+        <v>24.472690446146231</v>
+      </c>
+      <c r="M15" s="7">
+        <v>22.688930277955379</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>4</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G16" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="H6" s="7">
-        <v>2.4682266188321029</v>
-      </c>
-      <c r="I6" s="7">
-        <v>7.1431772282464863</v>
-      </c>
-      <c r="J6" s="7">
-        <v>0.51996534546714879</v>
-      </c>
-      <c r="K6" s="7">
-        <v>94.56840952735881</v>
-      </c>
-      <c r="L6" s="7">
-        <v>26.695252562823502</v>
-      </c>
-      <c r="M6" s="7">
-        <v>19.313250369876169</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
-        <v>7</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E7" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="H7" s="7">
-        <v>2.4756224951358652</v>
-      </c>
-      <c r="I7" s="7">
-        <v>7.1490489543975704</v>
-      </c>
-      <c r="J7" s="7">
-        <v>0.51917583950672985</v>
-      </c>
-      <c r="K7" s="7">
-        <v>94.513368707882478</v>
-      </c>
-      <c r="L7" s="7">
-        <v>26.63134854283771</v>
-      </c>
-      <c r="M7" s="7">
-        <v>19.017349431826961</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
-        <v>5</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="H8" s="7">
-        <v>2.4779713845906519</v>
-      </c>
-      <c r="I8" s="7">
-        <v>7.1506094042261932</v>
-      </c>
-      <c r="J8" s="7">
-        <v>0.51896591399936631</v>
-      </c>
-      <c r="K8" s="7">
-        <v>94.567253320598923</v>
-      </c>
-      <c r="L8" s="7">
-        <v>26.437840449680369</v>
-      </c>
-      <c r="M8" s="7">
-        <v>18.85858838573375</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
-        <v>5</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="H9" s="7">
-        <v>2.488888492807424</v>
-      </c>
-      <c r="I9" s="7">
-        <v>7.1553689678932049</v>
-      </c>
-      <c r="J9" s="7">
-        <v>0.51832533242163981</v>
-      </c>
-      <c r="K9" s="7">
-        <v>94.515573567285045</v>
-      </c>
-      <c r="L9" s="7">
-        <v>26.271968093180519</v>
-      </c>
-      <c r="M9" s="7">
-        <v>18.556201101443371</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="60" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
-        <v>7</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E10" s="2">
-        <v>0.9</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="H10" s="7">
-        <v>2.4627856480329191</v>
-      </c>
-      <c r="I10" s="7">
-        <v>7.1755828355908129</v>
-      </c>
-      <c r="J10" s="7">
-        <v>0.51560003318654712</v>
-      </c>
-      <c r="K10" s="7">
-        <v>94.933824640540692</v>
-      </c>
-      <c r="L10" s="7">
-        <v>26.766456588718821</v>
-      </c>
-      <c r="M10" s="7">
-        <v>19.074182179844762</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="60" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
-        <v>5</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="H11" s="7">
-        <v>2.4674289905153119</v>
-      </c>
-      <c r="I11" s="7">
-        <v>7.1790057368284206</v>
-      </c>
-      <c r="J11" s="7">
-        <v>0.51513778538125332</v>
-      </c>
-      <c r="K11" s="7">
-        <v>94.933932194657899</v>
-      </c>
-      <c r="L11" s="7">
-        <v>26.579553262812961</v>
-      </c>
-      <c r="M11" s="7">
-        <v>18.850248797709391</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
-        <v>7</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0.3</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="H12" s="7">
-        <v>2.4535201049942512</v>
-      </c>
-      <c r="I12" s="7">
-        <v>7.2159456000193831</v>
-      </c>
-      <c r="J12" s="7">
-        <v>0.51013519177434441</v>
-      </c>
-      <c r="K12" s="7">
-        <v>96.0551300893936</v>
-      </c>
-      <c r="L12" s="7">
-        <v>27.052025867512999</v>
-      </c>
-      <c r="M12" s="7">
-        <v>18.956192452981711</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
-        <v>5</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="H13" s="7">
-        <v>2.4604493754743428</v>
-      </c>
-      <c r="I13" s="7">
-        <v>7.2213972523929719</v>
-      </c>
-      <c r="J13" s="7">
-        <v>0.50939472570034172</v>
-      </c>
-      <c r="K13" s="7">
-        <v>96.0551300893936</v>
-      </c>
-      <c r="L13" s="7">
-        <v>26.917265440960911</v>
-      </c>
-      <c r="M13" s="7">
-        <v>18.896270968658591</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
-        <v>1</v>
-      </c>
-      <c r="B14" s="2" t="s">
+      <c r="H16" s="7">
+        <v>2.6232561371412531</v>
+      </c>
+      <c r="I16" s="7">
+        <v>7.3604526235800343</v>
+      </c>
+      <c r="J16" s="7">
+        <v>0.49031860193450633</v>
+      </c>
+      <c r="K16" s="7">
+        <v>94.560558076803318</v>
+      </c>
+      <c r="L16" s="7">
+        <v>24.839486774822628</v>
+      </c>
+      <c r="M16" s="7">
+        <v>19.504443147175191</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
         <v>4</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H14" s="7">
-        <v>2.8567363468837268</v>
-      </c>
-      <c r="I14" s="7">
-        <v>7.2216265848902577</v>
-      </c>
-      <c r="J14" s="7">
-        <v>0.50936356455095733</v>
-      </c>
-      <c r="K14" s="7">
-        <v>77.500108898543658</v>
-      </c>
-      <c r="L14" s="7">
-        <v>25.463811089751839</v>
-      </c>
-      <c r="M14" s="7">
-        <v>18.179684145825419</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="60" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
-        <v>7</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E15" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="H15" s="7">
-        <v>2.4524685374946378</v>
-      </c>
-      <c r="I15" s="7">
-        <v>7.227134393595164</v>
-      </c>
-      <c r="J15" s="7">
-        <v>0.50861487944270745</v>
-      </c>
-      <c r="K15" s="7">
-        <v>96.112510210918998</v>
-      </c>
-      <c r="L15" s="7">
-        <v>27.040090937216469</v>
-      </c>
-      <c r="M15" s="7">
-        <v>19.197113884796309</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="60" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
-        <v>5</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="H16" s="7">
-        <v>2.457807637536503</v>
-      </c>
-      <c r="I16" s="7">
-        <v>7.231196297621949</v>
-      </c>
-      <c r="J16" s="7">
-        <v>0.5080623727392648</v>
-      </c>
-      <c r="K16" s="7">
-        <v>96.112563987977609</v>
-      </c>
-      <c r="L16" s="7">
-        <v>26.918771791386689</v>
-      </c>
-      <c r="M16" s="7">
-        <v>19.03557297602832</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
-        <v>6</v>
-      </c>
       <c r="B17" s="2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>39</v>
@@ -1407,40 +1414,40 @@
       <c r="D17" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E17" s="2">
-        <v>0.5</v>
+      <c r="E17" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>46</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H17" s="7">
-        <v>2.6569306187208559</v>
+        <v>2.5506766195903761</v>
       </c>
       <c r="I17" s="7">
-        <v>7.2804051252924511</v>
+        <v>7.5698398165558478</v>
       </c>
       <c r="J17" s="7">
-        <v>0.50134424742944561</v>
+        <v>0.46090771177406492</v>
       </c>
       <c r="K17" s="7">
-        <v>94.506001250854382</v>
+        <v>94.931243341727935</v>
       </c>
       <c r="L17" s="7">
-        <v>24.779116884681919</v>
+        <v>25.900768586336479</v>
       </c>
       <c r="M17" s="7">
-        <v>23.051547920199411</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>12.242515219748141</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>4</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>39</v>
@@ -1455,33 +1462,33 @@
         <v>46</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H18" s="7">
-        <v>2.6770025161903162</v>
+        <v>2.64981685188704</v>
       </c>
       <c r="I18" s="7">
-        <v>7.2881507197461568</v>
+        <v>7.5745072714927417</v>
       </c>
       <c r="J18" s="7">
-        <v>0.50028264721540228</v>
+        <v>0.46024271363773023</v>
       </c>
       <c r="K18" s="7">
-        <v>94.507076792026368</v>
+        <v>96.11175733209862</v>
       </c>
       <c r="L18" s="7">
-        <v>24.472690446146231</v>
+        <v>27.01813298293305</v>
       </c>
       <c r="M18" s="7">
-        <v>22.688930277955379</v>
+        <v>26.25333197428936</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>39</v>
@@ -1489,122 +1496,122 @@
       <c r="D19" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E19" s="2">
-        <v>0.75</v>
+      <c r="E19" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>46</v>
       </c>
       <c r="G19" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="H19" s="7">
+        <v>2.7298484167170911</v>
+      </c>
+      <c r="I19" s="7">
+        <v>7.6201363267733608</v>
+      </c>
+      <c r="J19" s="7">
+        <v>0.453720098786627</v>
+      </c>
+      <c r="K19" s="7">
+        <v>96.054323433514625</v>
+      </c>
+      <c r="L19" s="7">
+        <v>26.81506535822751</v>
+      </c>
+      <c r="M19" s="7">
+        <v>28.84570835534058</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>5</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H20" s="7">
+        <v>2.488888492807424</v>
+      </c>
+      <c r="I20" s="7">
+        <v>7.1553689678932049</v>
+      </c>
+      <c r="J20" s="7">
+        <v>0.51832533242163981</v>
+      </c>
+      <c r="K20" s="7">
+        <v>94.515573567285045</v>
+      </c>
+      <c r="L20" s="7">
+        <v>26.271968093180519</v>
+      </c>
+      <c r="M20" s="7">
+        <v>18.556201101443371</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>5</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G21" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="H19" s="7">
-        <v>2.6065907643898489</v>
-      </c>
-      <c r="I19" s="7">
-        <v>7.342069801503941</v>
-      </c>
-      <c r="J19" s="7">
-        <v>0.49286129403783713</v>
-      </c>
-      <c r="K19" s="7">
-        <v>94.560665630920511</v>
-      </c>
-      <c r="L19" s="7">
-        <v>25.140003684764888</v>
-      </c>
-      <c r="M19" s="7">
-        <v>20.202806425807012</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
-        <v>4</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="H20" s="7">
-        <v>2.6232561371412531</v>
-      </c>
-      <c r="I20" s="7">
-        <v>7.3604526235800343</v>
-      </c>
-      <c r="J20" s="7">
-        <v>0.49031860193450633</v>
-      </c>
-      <c r="K20" s="7">
-        <v>94.560558076803318</v>
-      </c>
-      <c r="L20" s="7">
-        <v>24.839486774822628</v>
-      </c>
-      <c r="M20" s="7">
-        <v>19.504443147175191</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
-        <v>2</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>45</v>
-      </c>
       <c r="H21" s="7">
-        <v>3.1706289835191348</v>
+        <v>2.4779713845906519</v>
       </c>
       <c r="I21" s="7">
-        <v>7.5354277985963449</v>
+        <v>7.1506094042261932</v>
       </c>
       <c r="J21" s="7">
-        <v>0.4657979307309279</v>
+        <v>0.51896591399936631</v>
       </c>
       <c r="K21" s="7">
-        <v>6.9377514413596133</v>
+        <v>94.567253320598923</v>
       </c>
       <c r="L21" s="7">
-        <v>24.771411322888529</v>
+        <v>26.437840449680369</v>
       </c>
       <c r="M21" s="7">
-        <v>9.7119135648032326</v>
+        <v>18.85858838573375</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>39</v>
@@ -1612,40 +1619,40 @@
       <c r="D22" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E22" s="2">
-        <v>0.9</v>
+      <c r="E22" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G22" s="6" t="s">
         <v>51</v>
       </c>
       <c r="H22" s="7">
-        <v>2.5413627264017919</v>
+        <v>2.4674289905153119</v>
       </c>
       <c r="I22" s="7">
-        <v>7.5601813866822871</v>
+        <v>7.1790057368284206</v>
       </c>
       <c r="J22" s="7">
-        <v>0.46228250001114007</v>
+        <v>0.51513778538125332</v>
       </c>
       <c r="K22" s="7">
-        <v>94.931350895845128</v>
+        <v>94.933932194657899</v>
       </c>
       <c r="L22" s="7">
-        <v>26.147114817505649</v>
+        <v>26.579553262812961</v>
       </c>
       <c r="M22" s="7">
-        <v>12.523281349901319</v>
+        <v>18.850248797709391</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>39</v>
@@ -1653,40 +1660,40 @@
       <c r="D23" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E23" s="2">
-        <v>0.4</v>
+      <c r="E23" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G23" s="6" t="s">
         <v>52</v>
       </c>
       <c r="H23" s="7">
-        <v>2.6388373415659929</v>
+        <v>2.457807637536503</v>
       </c>
       <c r="I23" s="7">
-        <v>7.5624888465034994</v>
+        <v>7.231196297621949</v>
       </c>
       <c r="J23" s="7">
-        <v>0.46195421400563008</v>
+        <v>0.5080623727392648</v>
       </c>
       <c r="K23" s="7">
-        <v>96.111811109157202</v>
+        <v>96.112563987977609</v>
       </c>
       <c r="L23" s="7">
-        <v>27.20121249621964</v>
+        <v>26.918771791386689</v>
       </c>
       <c r="M23" s="7">
-        <v>26.342596453512972</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+        <v>19.03557297602832</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>39</v>
@@ -1698,36 +1705,36 @@
         <v>45</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H24" s="7">
-        <v>2.5506766195903761</v>
+        <v>2.4604493754743428</v>
       </c>
       <c r="I24" s="7">
-        <v>7.5698398165558478</v>
+        <v>7.2213972523929719</v>
       </c>
       <c r="J24" s="7">
-        <v>0.46090771177406492</v>
+        <v>0.50939472570034172</v>
       </c>
       <c r="K24" s="7">
-        <v>94.931243341727935</v>
+        <v>96.0551300893936</v>
       </c>
       <c r="L24" s="7">
-        <v>25.900768586336479</v>
+        <v>26.917265440960911</v>
       </c>
       <c r="M24" s="7">
-        <v>12.242515219748141</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+        <v>18.896270968658591</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>39</v>
@@ -1735,40 +1742,40 @@
       <c r="D25" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>45</v>
+      <c r="E25" s="2">
+        <v>0.5</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>46</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H25" s="7">
-        <v>2.64981685188704</v>
+        <v>2.6569306187208559</v>
       </c>
       <c r="I25" s="7">
-        <v>7.5745072714927417</v>
+        <v>7.2804051252924511</v>
       </c>
       <c r="J25" s="7">
-        <v>0.46024271363773023</v>
+        <v>0.50134424742944561</v>
       </c>
       <c r="K25" s="7">
-        <v>96.11175733209862</v>
+        <v>94.506001250854382</v>
       </c>
       <c r="L25" s="7">
-        <v>27.01813298293305</v>
+        <v>24.779116884681919</v>
       </c>
       <c r="M25" s="7">
-        <v>26.25333197428936</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+        <v>23.051547920199411</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>39</v>
@@ -1780,36 +1787,36 @@
         <v>0.75</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>50</v>
       </c>
       <c r="H26" s="7">
-        <v>2.833619405217993</v>
+        <v>2.6065907643898489</v>
       </c>
       <c r="I26" s="7">
-        <v>7.5817225415104001</v>
+        <v>7.342069801503941</v>
       </c>
       <c r="J26" s="7">
-        <v>0.45921390758597053</v>
+        <v>0.49286129403783713</v>
       </c>
       <c r="K26" s="7">
-        <v>85.090391168946539</v>
+        <v>94.560665630920511</v>
       </c>
       <c r="L26" s="7">
-        <v>27.183252164220011</v>
+        <v>25.140003684764888</v>
       </c>
       <c r="M26" s="7">
-        <v>21.108732784156022</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>20.202806425807012</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>6</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>39</v>
@@ -1818,39 +1825,39 @@
         <v>41</v>
       </c>
       <c r="E27" s="2">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>46</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H27" s="7">
-        <v>2.7161012925836912</v>
+        <v>2.5413627264017919</v>
       </c>
       <c r="I27" s="7">
-        <v>7.6105760128162601</v>
+        <v>7.5601813866822871</v>
       </c>
       <c r="J27" s="7">
-        <v>0.45508997747841889</v>
+        <v>0.46228250001114007</v>
       </c>
       <c r="K27" s="7">
-        <v>96.054377210573222</v>
+        <v>94.931350895845128</v>
       </c>
       <c r="L27" s="7">
-        <v>27.014714726197639</v>
+        <v>26.147114817505649</v>
       </c>
       <c r="M27" s="7">
-        <v>28.61745074237777</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>12.523281349901319</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>39</v>
@@ -1858,163 +1865,163 @@
       <c r="D28" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>45</v>
+      <c r="E28" s="2">
+        <v>0.4</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>46</v>
       </c>
       <c r="G28" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="H28" s="7">
+        <v>2.6388373415659929</v>
+      </c>
+      <c r="I28" s="7">
+        <v>7.5624888465034994</v>
+      </c>
+      <c r="J28" s="7">
+        <v>0.46195421400563008</v>
+      </c>
+      <c r="K28" s="7">
+        <v>96.111811109157202</v>
+      </c>
+      <c r="L28" s="7">
+        <v>27.20121249621964</v>
+      </c>
+      <c r="M28" s="7">
+        <v>26.342596453512972</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
+        <v>6</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E29" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G29" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="H28" s="7">
-        <v>2.7298484167170911</v>
-      </c>
-      <c r="I28" s="7">
-        <v>7.6201363267733608</v>
-      </c>
-      <c r="J28" s="7">
-        <v>0.453720098786627</v>
-      </c>
-      <c r="K28" s="7">
-        <v>96.054323433514625</v>
-      </c>
-      <c r="L28" s="7">
-        <v>26.81506535822751</v>
-      </c>
-      <c r="M28" s="7">
-        <v>28.84570835534058</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A29" s="2">
-        <v>2</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>45</v>
-      </c>
       <c r="H29" s="7">
-        <v>3.2163354847420331</v>
+        <v>2.7161012925836912</v>
       </c>
       <c r="I29" s="7">
-        <v>7.6333724393211861</v>
+        <v>7.6105760128162601</v>
       </c>
       <c r="J29" s="7">
-        <v>0.45182068341932141</v>
+        <v>0.45508997747841889</v>
       </c>
       <c r="K29" s="7">
-        <v>3.3728433382862</v>
+        <v>96.054377210573222</v>
       </c>
       <c r="L29" s="7">
-        <v>24.520661913551709</v>
+        <v>27.014714726197639</v>
       </c>
       <c r="M29" s="7">
-        <v>9.4536952096788642</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+        <v>28.61745074237777</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>45</v>
+      <c r="E30" s="2">
+        <v>0.5</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>49</v>
       </c>
       <c r="H30" s="7">
-        <v>3.226563230616541</v>
+        <v>2.4756224951358652</v>
       </c>
       <c r="I30" s="7">
-        <v>7.8592197344466506</v>
+        <v>7.1490489543975704</v>
       </c>
       <c r="J30" s="7">
-        <v>0.41890304107121262</v>
+        <v>0.51917583950672985</v>
       </c>
       <c r="K30" s="7">
-        <v>75.401539852295926</v>
+        <v>94.513368707882478</v>
       </c>
       <c r="L30" s="7">
-        <v>20.045932100675191</v>
+        <v>26.63134854283771</v>
       </c>
       <c r="M30" s="7">
-        <v>12.336412803429729</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+        <v>19.017349431826961</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E31" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="H31" s="7">
+        <v>2.4682266188321029</v>
+      </c>
+      <c r="I31" s="7">
+        <v>7.1431772282464863</v>
+      </c>
+      <c r="J31" s="7">
+        <v>0.51996534546714879</v>
+      </c>
+      <c r="K31" s="7">
+        <v>94.56840952735881</v>
+      </c>
+      <c r="L31" s="7">
+        <v>26.695252562823502</v>
+      </c>
+      <c r="M31" s="7">
+        <v>19.313250369876169</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
         <v>7</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H31" s="7">
-        <v>3.4996060522041521</v>
-      </c>
-      <c r="I31" s="7">
-        <v>8.2967692939284348</v>
-      </c>
-      <c r="J31" s="7">
-        <v>0.35239861643017739</v>
-      </c>
-      <c r="K31" s="7">
-        <v>9.305474665896579</v>
-      </c>
-      <c r="L31" s="7">
-        <v>21.806160509748981</v>
-      </c>
-      <c r="M31" s="7">
-        <v>5.0052971827636163</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A32" s="2">
-        <v>3</v>
-      </c>
       <c r="B32" s="2" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>39</v>
@@ -2026,110 +2033,110 @@
         <v>0.9</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>51</v>
       </c>
       <c r="H32" s="7">
-        <v>3.0278488612667172</v>
+        <v>2.4627856480329191</v>
       </c>
       <c r="I32" s="7">
-        <v>8.3225698872581546</v>
+        <v>7.1755828355908129</v>
       </c>
       <c r="J32" s="7">
-        <v>0.34836464159339908</v>
+        <v>0.51560003318654712</v>
       </c>
       <c r="K32" s="7">
-        <v>87.85165490831281</v>
+        <v>94.933824640540692</v>
       </c>
       <c r="L32" s="7">
-        <v>27.76788993908551</v>
+        <v>26.766456588718821</v>
       </c>
       <c r="M32" s="7">
-        <v>21.19707064248804</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+        <v>19.074182179844762</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E33" s="2" t="s">
-        <v>45</v>
+      <c r="E33" s="2">
+        <v>0.4</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>52</v>
       </c>
       <c r="H33" s="7">
-        <v>5.4602967883730509</v>
+        <v>2.4524685374946378</v>
       </c>
       <c r="I33" s="7">
-        <v>10.15019361435558</v>
+        <v>7.227134393595164</v>
       </c>
       <c r="J33" s="7">
-        <v>3.074423462670994E-2</v>
+        <v>0.50861487944270745</v>
       </c>
       <c r="K33" s="7">
-        <v>6.4286978046591363</v>
+        <v>96.112510210918998</v>
       </c>
       <c r="L33" s="7">
-        <v>11.641076090394931</v>
+        <v>27.040090937216469</v>
       </c>
       <c r="M33" s="7">
-        <v>0.47350327560485178</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+        <v>19.197113884796309</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
+      </c>
+      <c r="E34" s="2">
+        <v>0.3</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>53</v>
       </c>
       <c r="H34" s="7">
-        <v>4.4554620546761843</v>
+        <v>2.4535201049942512</v>
       </c>
       <c r="I34" s="7">
-        <v>10.32948531598924</v>
+        <v>7.2159456000193831</v>
       </c>
       <c r="J34" s="7">
-        <v>-3.7998009942659121E-3</v>
+        <v>0.51013519177434441</v>
       </c>
       <c r="K34" s="7">
-        <v>1.791690261351127</v>
+        <v>96.0551300893936</v>
       </c>
       <c r="L34" s="7">
-        <v>17.656280959846491</v>
+        <v>27.052025867512999</v>
       </c>
       <c r="M34" s="7">
-        <v>0.16215865602905891</v>
+        <v>18.956192452981711</v>
       </c>
     </row>
   </sheetData>
